--- a/samples/C_银行对账单.xlsx
+++ b/samples/C_银行对账单.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="银行对账单-工行" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="银行对账单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,14 +438,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,22 +458,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>余额</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>对账标记</t>
         </is>
       </c>
     </row>
@@ -483,15 +495,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>货款入账</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+          <t>记-001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>收到货款-重庆长安汽车</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>520000</v>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>3020000</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -502,15 +526,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>支付货款</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
+          <t>记-012</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>支付供应商款-重庆钢铁</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>380000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>2640000</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -521,15 +557,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>预付款入账</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+          <t>记-023</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>收到预付款-赛力斯集团</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>680000</v>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>3320000</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -540,15 +588,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>货款入账</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+          <t>记-047</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>收到货款-湖北双环科技</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>850000</v>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>4170000</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -559,15 +619,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>货款入账</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
+          <t>记-069</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>收到应收账款-四川长虹</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>720000</v>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>4890000</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -578,15 +650,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>投资款入账</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
+          <t>记-093</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>收到投资款-XX投资公司</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>6890000</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -597,15 +681,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>设备款支出</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>记-105</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>支付设备采购款-华为技术</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>1200000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>5690000</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -616,15 +712,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>补贴入账</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
+          <t>记-141</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>收到政府补贴</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>6190000</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -635,15 +743,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>货款入账</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
+          <t>记-189</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>收到货款-重庆川仪</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>620000</v>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>6810000</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -654,15 +774,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>货款入账</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
+          <t>记-237</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>收到货款-长安福特</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>350000</v>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>7160000</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -673,15 +805,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>奖金发放</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+          <t>记-273</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>支付年终奖</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>580000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>6580000</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -692,15 +836,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>利息入账</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
+          <t>记-285</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>收到银行利息</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>12000</v>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>6592000</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -711,15 +867,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>跨行转出</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>记-286</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>大额转账至建行两江支行</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>6092000</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -730,15 +898,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>银行存款利息(企业未记账)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
+          <t>银-001</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>银行利息收入(企业未入账)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>6095500</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未达</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -749,15 +929,58 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>账户管理费(企业未记账)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>银-002</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>账户管理费(企业未入账)</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>6094300</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未达</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>银-003</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>代收水电费(企业未入账)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6091500</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未达</t>
+        </is>
       </c>
     </row>
   </sheetData>
